--- a/data/wfa_sector_window_selection_2024-10-21_2026-04-20.xlsx
+++ b/data/wfa_sector_window_selection_2024-10-21_2026-04-20.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="4b7a5646-76f0-4ec1-addc-011cb4a" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="791e1440-815b-4c12-8e44-c946cd0" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -79,13 +79,13 @@
     <t xml:space="preserve">MA_Crossover_Signal</t>
   </si>
   <si>
+    <t xml:space="preserve">RSI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RSI_Signal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Finansial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RSI_Signal</t>
   </si>
   <si>
     <t xml:space="preserve">Industri</t>
@@ -439,34 +439,34 @@
         <v>45951</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J3" s="0" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K3" s="0" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L3" s="0" t="n">
-        <v>58.6206896551724</v>
+        <v>60.5263157894737</v>
       </c>
       <c r="M3" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N3" s="0" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="O3" s="0" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P3" s="0" t="n">
-        <v>62.5</v>
+        <v>63.6363636363636</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -489,34 +489,34 @@
         <v>46043</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H4" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J4" s="0" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="K4" s="0" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L4" s="0" t="n">
-        <v>63.6363636363636</v>
+        <v>68.421052631579</v>
       </c>
       <c r="M4" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N4" s="0" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O4" s="0" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P4" s="0" t="n">
-        <v>63.6363636363636</v>
+        <v>35.7142857142857</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -571,7 +571,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>1</v>
@@ -589,39 +589,39 @@
         <v>45859</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J6" s="0" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K6" s="0" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L6" s="0" t="n">
-        <v>43.3333333333333</v>
+        <v>43.75</v>
       </c>
       <c r="M6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N6" s="0" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O6" s="0" t="n">
         <v>10</v>
       </c>
       <c r="P6" s="0" t="n">
-        <v>55.5555555555556</v>
+        <v>66.6666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>2</v>
@@ -639,10 +639,10 @@
         <v>45951</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I7" s="0" t="n">
         <v>10</v>
@@ -651,27 +651,27 @@
         <v>30</v>
       </c>
       <c r="K7" s="0" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L7" s="0" t="n">
-        <v>46.6666666666667</v>
+        <v>50</v>
       </c>
       <c r="M7" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N7" s="0" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="O7" s="0" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="P7" s="0" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>3</v>
@@ -689,39 +689,39 @@
         <v>46043</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H8" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J8" s="0" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K8" s="0" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L8" s="0" t="n">
-        <v>51.2820512820513</v>
+        <v>54.1666666666667</v>
       </c>
       <c r="M8" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N8" s="0" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="O8" s="0" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="P8" s="0" t="n">
-        <v>57.1428571428571</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>4</v>
@@ -739,34 +739,34 @@
         <v>46133</v>
       </c>
       <c r="G9" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>47.3684210526316</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N9" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="J9" s="0" t="n">
-        <v>61</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>34</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <v>55.7377049180328</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <v>34</v>
-      </c>
       <c r="O9" s="0" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P9" s="0" t="n">
-        <v>38.2352941176471</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -789,10 +789,10 @@
         <v>45859</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H10" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I10" s="0" t="n">
         <v>10</v>
@@ -801,22 +801,22 @@
         <v>30</v>
       </c>
       <c r="K10" s="0" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L10" s="0" t="n">
+        <v>56.6666666666667</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="P10" s="0" t="n">
         <v>50</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="O10" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="P10" s="0" t="n">
-        <v>70</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -989,34 +989,34 @@
         <v>45859</v>
       </c>
       <c r="G14" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="0" t="s">
-        <v>21</v>
-      </c>
       <c r="I14" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J14" s="0" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="K14" s="0" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L14" s="0" t="n">
-        <v>52.7272727272727</v>
+        <v>63.8888888888889</v>
       </c>
       <c r="M14" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N14" s="0" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="O14" s="0" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="P14" s="0" t="n">
-        <v>47.0588235294118</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1039,34 +1039,34 @@
         <v>45951</v>
       </c>
       <c r="G15" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H15" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I15" s="0" t="n">
         <v>10</v>
       </c>
       <c r="J15" s="0" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="K15" s="0" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L15" s="0" t="n">
-        <v>51.6129032258065</v>
+        <v>53.8461538461539</v>
       </c>
       <c r="M15" s="0" t="n">
         <v>10</v>
       </c>
       <c r="N15" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="O15" s="0" t="n">
         <v>6</v>
       </c>
       <c r="P15" s="0" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
